--- a/ML Algorithm/data/_processed/Y labels/pressure_testing_vacp_workload.xlsx
+++ b/ML Algorithm/data/_processed/Y labels/pressure_testing_vacp_workload.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Operators" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Legend &amp; VACP Reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Step Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; VACP Reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operators'!$A$1:$K$177</definedName>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -120,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +161,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -902,11 +906,11 @@
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr"/>
@@ -992,11 +996,11 @@
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
@@ -1583,11 +1587,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -1857,11 +1861,11 @@
         </is>
       </c>
       <c r="I29" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr"/>
@@ -1902,11 +1906,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -2043,11 +2047,11 @@
         </is>
       </c>
       <c r="I33" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr"/>
@@ -2088,11 +2092,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -2229,11 +2233,11 @@
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr"/>
@@ -2274,11 +2278,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -2409,11 +2413,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -2638,11 +2642,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3887,11 +3891,11 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr"/>
@@ -3932,11 +3936,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2)</t>
+          <t>Manipulation (P4) — release radio button reclassified to background motor</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
@@ -5200,11 +5204,11 @@
         </is>
       </c>
       <c r="I102" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K102" s="8" t="inlineStr"/>
@@ -5245,11 +5249,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
@@ -5967,11 +5971,11 @@
         </is>
       </c>
       <c r="I119" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K119" s="8" t="inlineStr"/>
@@ -6012,11 +6016,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
@@ -7343,11 +7347,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
@@ -7388,11 +7392,11 @@
         </is>
       </c>
       <c r="I150" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr"/>
@@ -7705,11 +7709,11 @@
         </is>
       </c>
       <c r="I157" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr"/>
@@ -7936,11 +7940,11 @@
         </is>
       </c>
       <c r="I162" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K162" s="8" t="inlineStr"/>
@@ -7981,11 +7985,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
@@ -8120,11 +8124,11 @@
         </is>
       </c>
       <c r="I166" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K166" s="8" t="inlineStr"/>
@@ -8165,11 +8169,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
@@ -8306,11 +8310,11 @@
         </is>
       </c>
       <c r="I170" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K170" s="8" t="inlineStr"/>
@@ -8351,11 +8355,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
@@ -8535,11 +8539,11 @@
         </is>
       </c>
       <c r="I175" s="8" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>Interpret semantic content / speech (A5)</t>
+          <t>Speech (A1)</t>
         </is>
       </c>
       <c r="K175" s="8" t="inlineStr"/>
@@ -8580,11 +8584,11 @@
         </is>
       </c>
       <c r="I176" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>Discrete actuation (P2) [assumption]</t>
+          <t>Manipulation (P4) — release reclassified to background motor</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
@@ -8625,11 +8629,11 @@
         </is>
       </c>
       <c r="I177" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" s="7" t="inlineStr">
         <is>
-          <t>Automatic (C1)</t>
+          <t>No cognitive activity (C0)</t>
         </is>
       </c>
       <c r="K177" s="6" t="inlineStr"/>
@@ -8986,39 +8990,48 @@
   </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Step ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Step description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Operators</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>MWI_step</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>MWI_max_recorded</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>p_normalized</t>
         </is>
@@ -9042,13 +9055,13 @@
         <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>63.7</v>
+        <v>59.5</v>
       </c>
       <c r="F2" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>0.454351</v>
+        <v>0.464844</v>
       </c>
     </row>
     <row r="3">
@@ -9069,13 +9082,13 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>30.5</v>
+        <v>24.4</v>
       </c>
       <c r="F3" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.217546</v>
+        <v>0.190625</v>
       </c>
     </row>
     <row r="4">
@@ -9096,13 +9109,13 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>31.6</v>
+        <v>17.2</v>
       </c>
       <c r="F4" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>0.225392</v>
+        <v>0.134375</v>
       </c>
     </row>
     <row r="5">
@@ -9123,13 +9136,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>17.9</v>
+        <v>15.7</v>
       </c>
       <c r="F5" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>0.127675</v>
+        <v>0.122656</v>
       </c>
     </row>
     <row r="6">
@@ -9153,10 +9166,10 @@
         <v>8.6</v>
       </c>
       <c r="F6" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G6" t="n">
-        <v>0.061341</v>
+        <v>0.067187</v>
       </c>
     </row>
     <row r="7">
@@ -9180,10 +9193,10 @@
         <v>23.2</v>
       </c>
       <c r="F7" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.165478</v>
+        <v>0.18125</v>
       </c>
     </row>
     <row r="8">
@@ -9204,10 +9217,10 @@
         <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="F8" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -9234,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -9258,13 +9271,13 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>67.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
-        <v>0.478602</v>
+        <v>0.476562</v>
       </c>
     </row>
     <row r="11">
@@ -9288,10 +9301,10 @@
         <v>14.4</v>
       </c>
       <c r="F11" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>0.10271</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="12">
@@ -9315,10 +9328,10 @@
         <v>21.4</v>
       </c>
       <c r="F12" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.152639</v>
+        <v>0.167187</v>
       </c>
     </row>
     <row r="13">
@@ -9339,13 +9352,13 @@
         <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>50.3</v>
+        <v>47.1</v>
       </c>
       <c r="F13" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G13" t="n">
-        <v>0.358773</v>
+        <v>0.367969</v>
       </c>
     </row>
     <row r="14">
@@ -9366,13 +9379,13 @@
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>30.7</v>
+        <v>29.7</v>
       </c>
       <c r="F14" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G14" t="n">
-        <v>0.218973</v>
+        <v>0.232031</v>
       </c>
     </row>
     <row r="15">
@@ -9393,13 +9406,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>38.1</v>
+        <v>25.9</v>
       </c>
       <c r="F15" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G15" t="n">
-        <v>0.271755</v>
+        <v>0.202344</v>
       </c>
     </row>
     <row r="16">
@@ -9420,13 +9433,13 @@
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>32.5</v>
+        <v>19.3</v>
       </c>
       <c r="F16" t="n">
-        <v>140.2</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
-        <v>0.231812</v>
+        <v>0.150781</v>
       </c>
     </row>
   </sheetData>
